--- a/etf_holdings/2026-09-01_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-01_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>0006</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>60SK HYNIX INC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>60SK HYNIX INC</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.51%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.68%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>510000</v>
+        <v>21113</v>
       </c>
       <c r="K2" t="n">
-        <v>500000</v>
+        <v>11410</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>-9,703</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -559,123 +559,105 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>國巨股份</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>國巨股份</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7700000</v>
+        <v>31000</v>
       </c>
       <c r="K3" t="n">
-        <v>7500000</v>
+        <v>55000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>24,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>台灣積體</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>台灣積體</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>11.30%</t>
-        </is>
-      </c>
+          <t>09TX台指期貨</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>11.19%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4000000</v>
-      </c>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-200,000</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,55 +672,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1700000</v>
+        <v>58000</v>
       </c>
       <c r="K5" t="n">
-        <v>1600000</v>
+        <v>57000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -753,55 +735,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.97%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>4.41%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1400000</v>
+        <v>33000</v>
       </c>
       <c r="K6" t="n">
-        <v>1380000</v>
+        <v>32000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +798,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.82%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14000000</v>
+        <v>176000</v>
       </c>
       <c r="K7" t="n">
-        <v>13800000</v>
+        <v>175000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,55 +861,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.65%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1000000</v>
+        <v>1442000</v>
       </c>
       <c r="K8" t="n">
-        <v>900000</v>
+        <v>1435000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -937,60 +919,60 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>800000</v>
+        <v>111000</v>
       </c>
       <c r="K9" t="n">
-        <v>900000</v>
+        <v>110000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,55 +987,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2400000</v>
+        <v>245000</v>
       </c>
       <c r="K10" t="n">
-        <v>2000000</v>
+        <v>243000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-400,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1068,55 +1050,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>緯穎科技</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>緯穎科技</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>8.71%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>8.84%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>600000</v>
+        <v>381000</v>
       </c>
       <c r="K11" t="n">
-        <v>580000</v>
+        <v>378000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1131,55 +1113,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>360000</v>
+        <v>447000</v>
       </c>
       <c r="K12" t="n">
-        <v>300000</v>
+        <v>444000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-60,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1194,55 +1176,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0006</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60SK HYNIX INC</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60SK HYNIX INC</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21113</v>
+        <v>1619000</v>
       </c>
       <c r="K13" t="n">
-        <v>11410</v>
+        <v>1610000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-9,703</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-31_00990A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,53 +1234,53 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31000</v>
+        <v>152000</v>
       </c>
       <c r="K14" t="n">
-        <v>55000</v>
+        <v>151000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-31_00407A_full_holdings.xlsx</t>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1310,37 +1292,55 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09TX台指期貨</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.71%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>571000</v>
+      </c>
       <c r="K15" t="n">
-        <v>19</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>567000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-4,000</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>2026-08-31_00993A_full_holdings.xlsx</t>
@@ -1365,39 +1365,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>58000</v>
+        <v>23000</v>
       </c>
       <c r="K16" t="n">
-        <v>57000</v>
+        <v>22000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1428,39 +1428,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>33000</v>
+        <v>42000</v>
       </c>
       <c r="K17" t="n">
-        <v>32000</v>
+        <v>41000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1491,39 +1491,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>6.07%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>176000</v>
+        <v>115000</v>
       </c>
       <c r="K18" t="n">
-        <v>175000</v>
+        <v>114000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1554,43 +1554,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1442000</v>
+        <v>60000</v>
       </c>
       <c r="K19" t="n">
-        <v>1435000</v>
+        <v>59000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1617,43 +1617,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>111000</v>
+        <v>783000</v>
       </c>
       <c r="K20" t="n">
-        <v>110000</v>
+        <v>778000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1680,43 +1680,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>245000</v>
+        <v>103000</v>
       </c>
       <c r="K21" t="n">
-        <v>243000</v>
+        <v>102000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1743,43 +1743,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8.71%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8.84%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>381000</v>
+        <v>83000</v>
       </c>
       <c r="K22" t="n">
-        <v>378000</v>
+        <v>82000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1806,43 +1806,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>凱基金控</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>凱基金控</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>447000</v>
+        <v>1466000</v>
       </c>
       <c r="K23" t="n">
-        <v>444000</v>
+        <v>1458000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1869,43 +1869,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1619000</v>
+        <v>777360</v>
       </c>
       <c r="K24" t="n">
-        <v>1610000</v>
+        <v>773360</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1932,43 +1932,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>永豐金控</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>永豐金控</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>152000</v>
+        <v>1140220</v>
       </c>
       <c r="K25" t="n">
-        <v>151000</v>
+        <v>1134220</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1995,43 +1995,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>571000</v>
+        <v>159000</v>
       </c>
       <c r="K26" t="n">
-        <v>567000</v>
+        <v>158000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2058,43 +2058,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>23000</v>
+        <v>566000</v>
       </c>
       <c r="K27" t="n">
-        <v>22000</v>
+        <v>563000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2121,39 +2121,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>42000</v>
+        <v>26000</v>
       </c>
       <c r="K28" t="n">
-        <v>41000</v>
+        <v>25000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2184,43 +2184,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>115000</v>
+        <v>356000</v>
       </c>
       <c r="K29" t="n">
-        <v>114000</v>
+        <v>354000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2247,43 +2247,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>60000</v>
+        <v>262000</v>
       </c>
       <c r="K30" t="n">
-        <v>59000</v>
+        <v>260000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2310,43 +2310,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>783000</v>
+        <v>196000</v>
       </c>
       <c r="K31" t="n">
-        <v>778000</v>
+        <v>195000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2373,39 +2373,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創意電子</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創意電子</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>103000</v>
+        <v>49000</v>
       </c>
       <c r="K32" t="n">
-        <v>102000</v>
+        <v>48000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2436,39 +2436,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>83000</v>
+        <v>33000</v>
       </c>
       <c r="K33" t="n">
-        <v>82000</v>
+        <v>32000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2499,43 +2499,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>凱基金控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>凱基金控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1466000</v>
+        <v>37000</v>
       </c>
       <c r="K34" t="n">
-        <v>1458000</v>
+        <v>36000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2562,43 +2562,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>777360</v>
+        <v>9000</v>
       </c>
       <c r="K35" t="n">
-        <v>773360</v>
+        <v>8000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2625,43 +2625,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1140220</v>
+        <v>89000</v>
       </c>
       <c r="K36" t="n">
-        <v>1134220</v>
+        <v>88000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2688,43 +2688,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>159000</v>
+        <v>202000</v>
       </c>
       <c r="K37" t="n">
-        <v>158000</v>
+        <v>200000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2751,43 +2751,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>566000</v>
+        <v>26600</v>
       </c>
       <c r="K38" t="n">
-        <v>563000</v>
+        <v>25600</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2814,39 +2814,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>26000</v>
+        <v>95872</v>
       </c>
       <c r="K39" t="n">
-        <v>25000</v>
+        <v>94872</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2877,43 +2877,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>356000</v>
+        <v>49000</v>
       </c>
       <c r="K40" t="n">
-        <v>354000</v>
+        <v>48000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2940,43 +2940,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>262000</v>
+        <v>39000</v>
       </c>
       <c r="K41" t="n">
-        <v>260000</v>
+        <v>38000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3003,39 +3003,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>196000</v>
+        <v>80000</v>
       </c>
       <c r="K42" t="n">
-        <v>195000</v>
+        <v>79000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3066,39 +3066,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>創意電子</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>創意電子</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>49000</v>
+        <v>67000</v>
       </c>
       <c r="K43" t="n">
-        <v>48000</v>
+        <v>66000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3129,39 +3129,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>5.61%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>5.73%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>33000</v>
+        <v>116000</v>
       </c>
       <c r="K44" t="n">
-        <v>32000</v>
+        <v>115000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3192,43 +3192,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>37000</v>
+        <v>308000</v>
       </c>
       <c r="K45" t="n">
-        <v>36000</v>
+        <v>306000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3255,39 +3255,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>9000</v>
+        <v>40000</v>
       </c>
       <c r="K46" t="n">
-        <v>8000</v>
+        <v>39000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3318,39 +3318,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>89000</v>
+        <v>66000</v>
       </c>
       <c r="K47" t="n">
-        <v>88000</v>
+        <v>65000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3381,43 +3381,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>202000</v>
+        <v>56000</v>
       </c>
       <c r="K48" t="n">
-        <v>200000</v>
+        <v>55000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3444,39 +3444,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>26600</v>
+        <v>27000</v>
       </c>
       <c r="K49" t="n">
-        <v>25600</v>
+        <v>26000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3507,43 +3507,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>2.95%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>95872</v>
+        <v>249000</v>
       </c>
       <c r="K50" t="n">
-        <v>94872</v>
+        <v>247000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3570,39 +3570,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>49000</v>
+        <v>37000</v>
       </c>
       <c r="K51" t="n">
-        <v>48000</v>
+        <v>36000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3633,39 +3633,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>金居開發</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>金居開發</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>39000</v>
+        <v>88000</v>
       </c>
       <c r="K52" t="n">
-        <v>38000</v>
+        <v>87000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3696,39 +3696,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>80000</v>
+        <v>35000</v>
       </c>
       <c r="K53" t="n">
-        <v>79000</v>
+        <v>34000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3736,699 +3736,6 @@
         </is>
       </c>
       <c r="M53" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>6213</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0.36%</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>67000</v>
-      </c>
-      <c r="K54" t="n">
-        <v>66000</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>5.73%</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>+0.12%</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>116000</v>
-      </c>
-      <c r="K55" t="n">
-        <v>115000</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>4.23%</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>4.26%</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>308000</v>
-      </c>
-      <c r="K56" t="n">
-        <v>306000</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2.32%</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2.38%</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>40000</v>
-      </c>
-      <c r="K57" t="n">
-        <v>39000</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>6584</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>66000</v>
-      </c>
-      <c r="K58" t="n">
-        <v>65000</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>3.63%</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>3.79%</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>+0.16%</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>56000</v>
-      </c>
-      <c r="K59" t="n">
-        <v>55000</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-0.15%</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>27000</v>
-      </c>
-      <c r="K60" t="n">
-        <v>26000</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>3.06%</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2.95%</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>249000</v>
-      </c>
-      <c r="K61" t="n">
-        <v>247000</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>37000</v>
-      </c>
-      <c r="K62" t="n">
-        <v>36000</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>金居開發</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>金居開發</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0.41%</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>88000</v>
-      </c>
-      <c r="K63" t="n">
-        <v>87000</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K64" t="n">
-        <v>34000</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
         <is>
           <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-01_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-01_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0006</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>60SK HYNIX INC</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60SK HYNIX INC</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>8.51%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>8.68%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>21113</v>
+        <v>510000</v>
       </c>
       <c r="K2" t="n">
-        <v>11410</v>
+        <v>500000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-9,703</t>
+          <t>-10,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-31_00990A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -559,105 +559,123 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>國巨股份</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>國巨股份</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>5.01%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>31000</v>
+        <v>7700000</v>
       </c>
       <c r="K3" t="n">
-        <v>55000</v>
+        <v>7500000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-31_00407A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>台灣積體</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>09TX台指期貨</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>台灣積體</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>11.30%</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.71%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>11.19%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>4000000</v>
+      </c>
       <c r="K4" t="n">
-        <v>19</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>3800000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -672,55 +690,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>58000</v>
+        <v>1700000</v>
       </c>
       <c r="K5" t="n">
-        <v>57000</v>
+        <v>1600000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -735,55 +753,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>8.97%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>9.27%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33000</v>
+        <v>1400000</v>
       </c>
       <c r="K6" t="n">
-        <v>32000</v>
+        <v>1380000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -798,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>8.82%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>9.18%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>176000</v>
+        <v>14000000</v>
       </c>
       <c r="K7" t="n">
-        <v>175000</v>
+        <v>13800000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -861,55 +879,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1442000</v>
+        <v>1000000</v>
       </c>
       <c r="K8" t="n">
-        <v>1435000</v>
+        <v>900000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -919,60 +937,60 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>111000</v>
+        <v>800000</v>
       </c>
       <c r="K9" t="n">
-        <v>110000</v>
+        <v>900000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -987,55 +1005,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>245000</v>
+        <v>2400000</v>
       </c>
       <c r="K10" t="n">
-        <v>243000</v>
+        <v>2000000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-400,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1050,55 +1068,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯穎科技</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯穎科技</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.71%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.84%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>381000</v>
+        <v>600000</v>
       </c>
       <c r="K11" t="n">
-        <v>378000</v>
+        <v>580000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1113,55 +1131,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>鴻勁精密</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>鴻勁精密</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>447000</v>
+        <v>360000</v>
       </c>
       <c r="K12" t="n">
-        <v>444000</v>
+        <v>300000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-60,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1176,55 +1194,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>0006</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>60SK HYNIX INC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>60SK HYNIX INC</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1619000</v>
+        <v>21113</v>
       </c>
       <c r="K13" t="n">
-        <v>1610000</v>
+        <v>11410</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>-9,703</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1234,53 +1252,53 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>152000</v>
+        <v>31000</v>
       </c>
       <c r="K14" t="n">
-        <v>151000</v>
+        <v>55000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>24,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+          <t>2026-08-31_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1302,43 +1320,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>571000</v>
+        <v>58000</v>
       </c>
       <c r="K15" t="n">
-        <v>567000</v>
+        <v>57000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1365,39 +1383,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>4.41%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>23000</v>
+        <v>33000</v>
       </c>
       <c r="K16" t="n">
-        <v>22000</v>
+        <v>32000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1428,39 +1446,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>42000</v>
+        <v>176000</v>
       </c>
       <c r="K17" t="n">
-        <v>41000</v>
+        <v>175000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1491,43 +1509,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>115000</v>
+        <v>1442000</v>
       </c>
       <c r="K18" t="n">
-        <v>114000</v>
+        <v>1435000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1554,39 +1572,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>60000</v>
+        <v>111000</v>
       </c>
       <c r="K19" t="n">
-        <v>59000</v>
+        <v>110000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1617,43 +1635,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>783000</v>
+        <v>245000</v>
       </c>
       <c r="K20" t="n">
-        <v>778000</v>
+        <v>243000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1680,43 +1698,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>8.71%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>8.84%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>103000</v>
+        <v>381000</v>
       </c>
       <c r="K21" t="n">
-        <v>102000</v>
+        <v>378000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1743,43 +1761,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>83000</v>
+        <v>447000</v>
       </c>
       <c r="K22" t="n">
-        <v>82000</v>
+        <v>444000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1806,43 +1824,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>凱基金控</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>凱基金控</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1466000</v>
+        <v>1619000</v>
       </c>
       <c r="K23" t="n">
-        <v>1458000</v>
+        <v>1610000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1869,43 +1887,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>777360</v>
+        <v>152000</v>
       </c>
       <c r="K24" t="n">
-        <v>773360</v>
+        <v>151000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1932,43 +1950,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1140220</v>
+        <v>571000</v>
       </c>
       <c r="K25" t="n">
-        <v>1134220</v>
+        <v>567000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1995,39 +2013,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>159000</v>
+        <v>23000</v>
       </c>
       <c r="K26" t="n">
-        <v>158000</v>
+        <v>22000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2058,43 +2076,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>566000</v>
+        <v>42000</v>
       </c>
       <c r="K27" t="n">
-        <v>563000</v>
+        <v>41000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2121,39 +2139,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>6.07%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>26000</v>
+        <v>115000</v>
       </c>
       <c r="K28" t="n">
-        <v>25000</v>
+        <v>114000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2184,43 +2202,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>356000</v>
+        <v>60000</v>
       </c>
       <c r="K29" t="n">
-        <v>354000</v>
+        <v>59000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2247,43 +2265,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>262000</v>
+        <v>783000</v>
       </c>
       <c r="K30" t="n">
-        <v>260000</v>
+        <v>778000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2310,39 +2328,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>196000</v>
+        <v>103000</v>
       </c>
       <c r="K31" t="n">
-        <v>195000</v>
+        <v>102000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2373,39 +2391,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>創意電子</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>創意電子</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>49000</v>
+        <v>83000</v>
       </c>
       <c r="K32" t="n">
-        <v>48000</v>
+        <v>82000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2436,17 +2454,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>凱基金控</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>凱基金控</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2456,23 +2474,23 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>33000</v>
+        <v>1466000</v>
       </c>
       <c r="K33" t="n">
-        <v>32000</v>
+        <v>1458000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2499,43 +2517,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>37000</v>
+        <v>777360</v>
       </c>
       <c r="K34" t="n">
-        <v>36000</v>
+        <v>773360</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2562,43 +2580,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>永豐金控</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>永豐金控</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>9000</v>
+        <v>1140220</v>
       </c>
       <c r="K35" t="n">
-        <v>8000</v>
+        <v>1134220</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2625,39 +2643,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>89000</v>
+        <v>159000</v>
       </c>
       <c r="K36" t="n">
-        <v>88000</v>
+        <v>158000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2688,43 +2706,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>202000</v>
+        <v>566000</v>
       </c>
       <c r="K37" t="n">
-        <v>200000</v>
+        <v>563000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2751,39 +2769,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>26600</v>
+        <v>26000</v>
       </c>
       <c r="K38" t="n">
-        <v>25600</v>
+        <v>25000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2814,43 +2832,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>95872</v>
+        <v>356000</v>
       </c>
       <c r="K39" t="n">
-        <v>94872</v>
+        <v>354000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2877,43 +2895,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>49000</v>
+        <v>262000</v>
       </c>
       <c r="K40" t="n">
-        <v>48000</v>
+        <v>260000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2940,39 +2958,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>39000</v>
+        <v>196000</v>
       </c>
       <c r="K41" t="n">
-        <v>38000</v>
+        <v>195000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3003,39 +3021,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創意電子</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創意電子</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>80000</v>
+        <v>49000</v>
       </c>
       <c r="K42" t="n">
-        <v>79000</v>
+        <v>48000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3066,39 +3084,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>67000</v>
+        <v>33000</v>
       </c>
       <c r="K43" t="n">
-        <v>66000</v>
+        <v>32000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3129,39 +3147,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>116000</v>
+        <v>37000</v>
       </c>
       <c r="K44" t="n">
-        <v>115000</v>
+        <v>36000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3192,43 +3210,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>308000</v>
+        <v>9000</v>
       </c>
       <c r="K45" t="n">
-        <v>306000</v>
+        <v>8000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3255,39 +3273,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>40000</v>
+        <v>89000</v>
       </c>
       <c r="K46" t="n">
-        <v>39000</v>
+        <v>88000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3318,43 +3336,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>66000</v>
+        <v>202000</v>
       </c>
       <c r="K47" t="n">
-        <v>65000</v>
+        <v>200000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3381,39 +3399,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>56000</v>
+        <v>26600</v>
       </c>
       <c r="K48" t="n">
-        <v>55000</v>
+        <v>25600</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3444,39 +3462,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>27000</v>
+        <v>95872</v>
       </c>
       <c r="K49" t="n">
-        <v>26000</v>
+        <v>94872</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3507,43 +3525,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>249000</v>
+        <v>49000</v>
       </c>
       <c r="K50" t="n">
-        <v>247000</v>
+        <v>48000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3570,39 +3588,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>37000</v>
+        <v>39000</v>
       </c>
       <c r="K51" t="n">
-        <v>36000</v>
+        <v>38000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3633,39 +3651,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>金居開發</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>金居開發</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>88000</v>
+        <v>80000</v>
       </c>
       <c r="K52" t="n">
-        <v>87000</v>
+        <v>79000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3696,46 +3714,676 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>67000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>66000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5.73%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>116000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4.23%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>308000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>306000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2.32%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>39000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>55000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>27000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>3.06%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2.95%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>249000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>247000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>37000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>88000</v>
+      </c>
+      <c r="K62" t="n">
+        <v>87000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>0.44%</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>0.39%</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>-0.05%</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J63" t="n">
         <v>35000</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K63" t="n">
         <v>34000</v>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-1,000</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-01_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-01_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,63 +486,4937 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1644000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2157000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>513,000</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-08-31_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>3173000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2838000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-335,000</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-08-31_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>54000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>53,000</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-08-31_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>聯華電子</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>漢唐集成</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>川湖科技</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>川湖科技</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8.54%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>510000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>國巨股份</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>國巨股份</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5.37%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5.14%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>7700000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>台灣積體</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>台灣積體</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11.30%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>11.19%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4.22%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8.97%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>9.39%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>南亞科技</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>南亞科技</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8.82%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8.63%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>聯發科技</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>聯發科技</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4.65%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4.69%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>900000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.72%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>800000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>900000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.67%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-400,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5.04%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>600000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>580000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>360000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>727000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>627000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-08-31_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-08-31_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.64%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>長興</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>長興</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>9785000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-1,785,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>16.22%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>15.86%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.36%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-1,500,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-5,000,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,200,000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>860000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>460,000</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2.51%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-1,000,000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2.72%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+0.88%</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>639000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>968000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>329,000</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-08-31_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>21113</v>
+      </c>
+      <c r="K30" t="n">
+        <v>11410</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-9,703</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-08-31_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>00407A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>3008</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>0.81%</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>1.60%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>+0.79%</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J31" t="n">
         <v>31000</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K31" t="n">
         <v>55000</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>24,000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>2026-08-31_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>57000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>33000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>176000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>175000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+0.18%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1442000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1435000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>台達電子</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>台達電子</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>111000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>243000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>8.71%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>8.84%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>381000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>378000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>447000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>444000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1619000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>152000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>151000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>571000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>567000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-4,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>42000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>41000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>115000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>59000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>783000</v>
+      </c>
+      <c r="K47" t="n">
+        <v>778000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>3.89%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>103000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>83000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1466000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1458000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>777360</v>
+      </c>
+      <c r="K51" t="n">
+        <v>773360</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-4,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1140220</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1134220</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>5.05%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5.26%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>159000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>158000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>6.35%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-0.89%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>566000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>563000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>356000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>354000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>262000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>260000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>196000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>195000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>48000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>33000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>37000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>9000</v>
+      </c>
+      <c r="K62" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>89000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>88000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>202000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>3.87%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>26600</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25600</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>95872</v>
+      </c>
+      <c r="K66" t="n">
+        <v>94872</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>48000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>39000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>38000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>79000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>67000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>66000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>5.73%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>116000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4.23%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>308000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>306000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2.32%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>39000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>55000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>27000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>3.06%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2.95%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>249000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>247000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>37000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>88000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>87000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-01_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-01_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,133 +675,97 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1.64%</t>
-        </is>
-      </c>
+          <t>聯華電子</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>11000000</v>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1,000,000</t>
-        </is>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>長興</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>長興</t>
-        </is>
-      </c>
+          <t>漢唐集成</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.14%</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>300,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +780,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>8.51%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>8.54%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9785000</v>
+        <v>510000</v>
       </c>
       <c r="K7" t="n">
-        <v>8000000</v>
+        <v>500000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-1,785,000</t>
+          <t>-10,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,39 +843,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨股份</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨股份</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>16.22%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.86%</t>
+          <t>5.14%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11000000</v>
+        <v>7700000</v>
       </c>
       <c r="K8" t="n">
-        <v>10800000</v>
+        <v>7500000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -920,14 +884,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,55 +906,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>11.19%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4500000</v>
+        <v>4000000</v>
       </c>
       <c r="K9" t="n">
-        <v>3000000</v>
+        <v>3800000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1,500,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,55 +969,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>12000000</v>
+        <v>1700000</v>
       </c>
       <c r="K10" t="n">
-        <v>7000000</v>
+        <v>1600000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-5,000,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,60 +1027,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>8.97%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>9.39%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>500000</v>
+        <v>1400000</v>
       </c>
       <c r="K11" t="n">
-        <v>1700000</v>
+        <v>1380000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,60 +1090,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>8.82%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>8.63%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>400000</v>
+        <v>14000000</v>
       </c>
       <c r="K12" t="n">
-        <v>860000</v>
+        <v>13800000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>460,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1194,111 +1158,4265 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>4.69%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="K13" t="n">
-        <v>6000000</v>
+        <v>900000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-1,000,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.72%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>800000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>900000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.67%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-400,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5.04%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>600000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>580000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>360000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08-31_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>727000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>627000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-08-31_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-08-31_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.64%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>長興</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>長興</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>9785000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-1,785,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>16.22%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>15.86%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.36%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-1,500,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-5,000,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,200,000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>860000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>460,000</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2.51%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-1,000,000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-08-31_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>00992A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>8046</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>南電</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>1.84%</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2.72%</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>+0.88%</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J29" t="n">
         <v>639000</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K29" t="n">
         <v>968000</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>329,000</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>2026-08-31_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>21113</v>
+      </c>
+      <c r="K30" t="n">
+        <v>11410</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-9,703</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-08-31_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>+0.79%</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>55000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>24,000</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-08-31_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>57000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>33000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>176000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>175000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+0.18%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1442000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1435000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>台達電子</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>台達電子</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>111000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>243000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>8.71%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>8.84%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>381000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>378000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>447000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>444000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1619000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>152000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>151000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>571000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>567000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-4,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>42000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>41000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>115000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>59000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>783000</v>
+      </c>
+      <c r="K47" t="n">
+        <v>778000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>3.89%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>103000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>83000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1466000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1458000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>777360</v>
+      </c>
+      <c r="K51" t="n">
+        <v>773360</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-4,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1140220</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1134220</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>5.05%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5.26%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>159000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>158000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>6.35%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-0.89%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>566000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>563000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>356000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>354000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>262000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>260000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>196000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>195000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>48000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>33000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>37000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>9000</v>
+      </c>
+      <c r="K62" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>89000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>88000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>202000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>3.87%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>26600</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25600</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>95872</v>
+      </c>
+      <c r="K66" t="n">
+        <v>94872</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>48000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>39000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>38000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>79000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>67000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>66000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>5.73%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>116000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4.23%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>308000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>306000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2.32%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>39000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>55000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>27000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>3.06%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2.95%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>249000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>247000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>37000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>88000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>87000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08-31_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
